--- a/VerveStacks_GBR_grids_kan10/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_GBR_grids_kan10/ReportDefs_vervestacks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CA6C381-E357-4533-9AD9-24A590504BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A5A430-EB94-4123-8A29-CFAA6AD3BE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6569" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6558" uniqueCount="676">
   <si>
     <t>Unit</t>
   </si>
@@ -1228,60 +1228,57 @@
     <t>grid_node</t>
   </si>
   <si>
+    <t>p_w1262971878_GBR</t>
+  </si>
+  <si>
+    <t>p_w1274396508-400_GBR</t>
+  </si>
+  <si>
+    <t>p_w137050527_GBR</t>
+  </si>
+  <si>
+    <t>p_w148382435_GBR</t>
+  </si>
+  <si>
+    <t>p_w25422135-400_GBR</t>
+  </si>
+  <si>
+    <t>p_w297840585_GBR</t>
+  </si>
+  <si>
+    <t>p_w375626500_GBR</t>
+  </si>
+  <si>
+    <t>p_w568527671_GBR</t>
+  </si>
+  <si>
+    <t>p_w975637991_GBR</t>
+  </si>
+  <si>
     <t>p_r10695345_GBR</t>
   </si>
   <si>
     <t>p_w1078532568_GBR</t>
   </si>
   <si>
+    <t>p_w109189896_GBR</t>
+  </si>
+  <si>
     <t>p_w23281217_GBR</t>
   </si>
   <si>
+    <t>p_w536905500_GBR</t>
+  </si>
+  <si>
     <t>p_w636630368_GBR</t>
   </si>
   <si>
+    <t>p_w642490160_GBR</t>
+  </si>
+  <si>
     <t>p_w775577829_GBR</t>
   </si>
   <si>
-    <t>p_w1262971878_GBR</t>
-  </si>
-  <si>
-    <t>p_w1274396508-400_GBR</t>
-  </si>
-  <si>
-    <t>p_w137050527_GBR</t>
-  </si>
-  <si>
-    <t>p_w148382435_GBR</t>
-  </si>
-  <si>
-    <t>p_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>p_w297840585_GBR</t>
-  </si>
-  <si>
-    <t>p_w375626500_GBR</t>
-  </si>
-  <si>
-    <t>p_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>p_w975637991_GBR</t>
-  </si>
-  <si>
-    <t>p_w109189896_GBR</t>
-  </si>
-  <si>
-    <t>p_w536905500_GBR</t>
-  </si>
-  <si>
-    <t>p_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>p_w227767019-275_GBR</t>
-  </si>
-  <si>
     <t>rez_spv_GBR_001</t>
   </si>
   <si>
@@ -1513,24 +1510,24 @@
     <t>admin_1</t>
   </si>
   <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>Northern Ireland</t>
+  </si>
+  <si>
+    <t>East of England</t>
+  </si>
+  <si>
     <t>South East (England)</t>
   </si>
   <si>
     <t>East Midlands (England)</t>
   </si>
   <si>
-    <t>Scotland</t>
-  </si>
-  <si>
-    <t>Wales</t>
-  </si>
-  <si>
-    <t>Northern Ireland</t>
-  </si>
-  <si>
-    <t>East of England</t>
-  </si>
-  <si>
     <t>North East (England)</t>
   </si>
   <si>
@@ -1549,60 +1546,57 @@
     <t>region_com</t>
   </si>
   <si>
+    <t>e_w1262971878_GBR</t>
+  </si>
+  <si>
+    <t>e_w1274396508-400_GBR</t>
+  </si>
+  <si>
+    <t>e_w137050527_GBR</t>
+  </si>
+  <si>
+    <t>e_w148382435_GBR</t>
+  </si>
+  <si>
+    <t>e_w25422135-400_GBR</t>
+  </si>
+  <si>
+    <t>e_w297840585_GBR</t>
+  </si>
+  <si>
+    <t>e_w375626500_GBR</t>
+  </si>
+  <si>
+    <t>e_w568527671_GBR</t>
+  </si>
+  <si>
+    <t>e_w975637991_GBR</t>
+  </si>
+  <si>
     <t>e_r10695345_GBR</t>
   </si>
   <si>
     <t>e_w1078532568_GBR</t>
   </si>
   <si>
+    <t>e_w109189896_GBR</t>
+  </si>
+  <si>
     <t>e_w23281217_GBR</t>
   </si>
   <si>
+    <t>e_w536905500_GBR</t>
+  </si>
+  <si>
     <t>e_w636630368_GBR</t>
   </si>
   <si>
+    <t>e_w642490160_GBR</t>
+  </si>
+  <si>
     <t>e_w775577829_GBR</t>
   </si>
   <si>
-    <t>e_w1262971878_GBR</t>
-  </si>
-  <si>
-    <t>e_w1274396508-400_GBR</t>
-  </si>
-  <si>
-    <t>e_w137050527_GBR</t>
-  </si>
-  <si>
-    <t>e_w148382435_GBR</t>
-  </si>
-  <si>
-    <t>e_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR</t>
-  </si>
-  <si>
-    <t>e_w375626500_GBR</t>
-  </si>
-  <si>
-    <t>e_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>e_w975637991_GBR</t>
-  </si>
-  <si>
-    <t>e_w109189896_GBR</t>
-  </si>
-  <si>
-    <t>e_w536905500_GBR</t>
-  </si>
-  <si>
-    <t>e_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>e_w227767019-275_GBR</t>
-  </si>
-  <si>
     <t>elc_spv_GBR_001</t>
   </si>
   <si>
@@ -1840,58 +1834,55 @@
     <t>lng</t>
   </si>
   <si>
+    <t>GBR-e_w1262971878_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w1274396508-400_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w137050527_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w148382435_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w25422135-400_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w297840585_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w375626500_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w568527671_GBR</t>
+  </si>
+  <si>
+    <t>GBR-e_w975637991_GBR</t>
+  </si>
+  <si>
     <t>GBR-e_r10695345_GBR</t>
   </si>
   <si>
     <t>GBR-e_w1078532568_GBR</t>
   </si>
   <si>
+    <t>GBR-e_w109189896_GBR</t>
+  </si>
+  <si>
     <t>GBR-e_w23281217_GBR</t>
   </si>
   <si>
+    <t>GBR-e_w536905500_GBR</t>
+  </si>
+  <si>
     <t>GBR-e_w636630368_GBR</t>
   </si>
   <si>
+    <t>GBR-e_w642490160_GBR</t>
+  </si>
+  <si>
     <t>GBR-e_w775577829_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w1262971878_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w1274396508-400_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w137050527_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w148382435_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w297840585_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w375626500_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w975637991_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w109189896_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w536905500_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>GBR-e_w227767019-275_GBR</t>
   </si>
   <si>
     <t>GBR-elc_spv_GBR_001</t>
@@ -25312,16 +25303,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC44ECF-64DB-4ACC-A5DC-D0F590E6AE8A}">
-  <dimension ref="B9:H104"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE4CE3D8-D05A-432E-B8BB-3A70D61025E6}">
+  <dimension ref="B9:H103"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F9" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -25329,19 +25320,19 @@
         <v>373</v>
       </c>
       <c r="C10" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F10" t="s">
         <v>373</v>
       </c>
       <c r="G10" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -25349,19 +25340,19 @@
         <v>381</v>
       </c>
       <c r="C11">
-        <v>51.309878141456501</v>
+        <v>58.479967903761491</v>
       </c>
       <c r="D11">
-        <v>1.3456388979917795</v>
+        <v>-3.4521849436940708</v>
       </c>
       <c r="F11" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G11">
-        <v>51.309878141456501</v>
+        <v>58.479967903761491</v>
       </c>
       <c r="H11">
-        <v>1.3456388979917795</v>
+        <v>-3.4521849436940708</v>
       </c>
     </row>
     <row r="12" spans="2:8">
@@ -25369,19 +25360,19 @@
         <v>382</v>
       </c>
       <c r="C12">
-        <v>52.9209925331145</v>
+        <v>53.229726628324848</v>
       </c>
       <c r="D12">
-        <v>-0.2365005345670102</v>
+        <v>-3.0742279809374224</v>
       </c>
       <c r="F12" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G12">
-        <v>52.9209925331145</v>
+        <v>53.229726628324848</v>
       </c>
       <c r="H12">
-        <v>-0.2365005345670102</v>
+        <v>-3.0742279809374224</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -25389,19 +25380,19 @@
         <v>383</v>
       </c>
       <c r="C13">
-        <v>51.105578116437883</v>
+        <v>54.843201485290322</v>
       </c>
       <c r="D13">
-        <v>0.97511944977862963</v>
+        <v>-5.7704690130982392</v>
       </c>
       <c r="F13" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G13">
-        <v>51.105578116437883</v>
+        <v>54.843201485290322</v>
       </c>
       <c r="H13">
-        <v>0.97511944977862963</v>
+        <v>-5.7704690130982392</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -25409,19 +25400,19 @@
         <v>384</v>
       </c>
       <c r="C14">
-        <v>50.818035638860259</v>
+        <v>55.069699109090998</v>
       </c>
       <c r="D14">
-        <v>-1.194439480272105</v>
+        <v>-4.9807507247075335</v>
       </c>
       <c r="F14" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G14">
-        <v>50.818035638860259</v>
+        <v>55.069699109090998</v>
       </c>
       <c r="H14">
-        <v>-1.194439480272105</v>
+        <v>-4.9807507247075335</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -25429,19 +25420,19 @@
         <v>385</v>
       </c>
       <c r="C15">
-        <v>51.09844688040387</v>
+        <v>52.071398122643167</v>
       </c>
       <c r="D15">
-        <v>1.1448358124246545</v>
+        <v>1.0618678452808807</v>
       </c>
       <c r="F15" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G15">
-        <v>51.09844688040387</v>
+        <v>52.071398122643167</v>
       </c>
       <c r="H15">
-        <v>1.1448358124246545</v>
+        <v>1.0618678452808807</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -25449,19 +25440,19 @@
         <v>386</v>
       </c>
       <c r="C16">
-        <v>58.479967903761491</v>
+        <v>55.718036768358985</v>
       </c>
       <c r="D16">
-        <v>-3.4521849436940708</v>
+        <v>-4.8948211898549143</v>
       </c>
       <c r="F16" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G16">
-        <v>58.479967903761491</v>
+        <v>55.718036768358985</v>
       </c>
       <c r="H16">
-        <v>-3.4521849436940708</v>
+        <v>-4.8948211898549143</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -25469,19 +25460,19 @@
         <v>387</v>
       </c>
       <c r="C17">
-        <v>53.229726628324848</v>
+        <v>53.230462688056122</v>
       </c>
       <c r="D17">
-        <v>-3.0742279809374224</v>
+        <v>-3.0325941174955027</v>
       </c>
       <c r="F17" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G17">
-        <v>53.229726628324848</v>
+        <v>53.230462688056122</v>
       </c>
       <c r="H17">
-        <v>-3.0742279809374224</v>
+        <v>-3.0325941174955027</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -25489,19 +25480,19 @@
         <v>388</v>
       </c>
       <c r="C18">
-        <v>54.843201485290322</v>
+        <v>57.521174967011859</v>
       </c>
       <c r="D18">
-        <v>-5.7704690130982392</v>
+        <v>-2.9504139962807976</v>
       </c>
       <c r="F18" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G18">
-        <v>54.843201485290322</v>
+        <v>57.521174967011859</v>
       </c>
       <c r="H18">
-        <v>-5.7704690130982392</v>
+        <v>-2.9504139962807976</v>
       </c>
     </row>
     <row r="19" spans="2:8">
@@ -25509,19 +25500,19 @@
         <v>389</v>
       </c>
       <c r="C19">
-        <v>55.069699109090998</v>
+        <v>60.29340062591924</v>
       </c>
       <c r="D19">
-        <v>-4.9807507247075335</v>
+        <v>-1.2719451172071998</v>
       </c>
       <c r="F19" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G19">
-        <v>55.069699109090998</v>
+        <v>60.29340062591924</v>
       </c>
       <c r="H19">
-        <v>-4.9807507247075335</v>
+        <v>-1.2719451172071998</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -25529,19 +25520,19 @@
         <v>390</v>
       </c>
       <c r="C20">
-        <v>52.071398122643167</v>
+        <v>51.309878141456501</v>
       </c>
       <c r="D20">
-        <v>1.0618678452808807</v>
+        <v>1.3456388979917795</v>
       </c>
       <c r="F20" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G20">
-        <v>52.071398122643167</v>
+        <v>51.309878141456501</v>
       </c>
       <c r="H20">
-        <v>1.0618678452808807</v>
+        <v>1.3456388979917795</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -25549,19 +25540,19 @@
         <v>391</v>
       </c>
       <c r="C21">
-        <v>55.718036768358985</v>
+        <v>52.9209925331145</v>
       </c>
       <c r="D21">
-        <v>-4.8948211898549143</v>
+        <v>-0.2365005345670102</v>
       </c>
       <c r="F21" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G21">
-        <v>55.718036768358985</v>
+        <v>52.9209925331145</v>
       </c>
       <c r="H21">
-        <v>-4.8948211898549143</v>
+        <v>-0.2365005345670102</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -25569,19 +25560,19 @@
         <v>392</v>
       </c>
       <c r="C22">
-        <v>53.230462688056122</v>
+        <v>51.440498299145609</v>
       </c>
       <c r="D22">
-        <v>-3.0325941174955027</v>
+        <v>0.71615754360028872</v>
       </c>
       <c r="F22" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G22">
-        <v>53.230462688056122</v>
+        <v>51.440498299145609</v>
       </c>
       <c r="H22">
-        <v>-3.0325941174955027</v>
+        <v>0.71615754360028872</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -25589,19 +25580,19 @@
         <v>393</v>
       </c>
       <c r="C23">
-        <v>57.521174967011859</v>
+        <v>51.105578116437883</v>
       </c>
       <c r="D23">
-        <v>-2.9504139962807976</v>
+        <v>0.97511944977862963</v>
       </c>
       <c r="F23" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G23">
-        <v>57.521174967011859</v>
+        <v>51.105578116437883</v>
       </c>
       <c r="H23">
-        <v>-2.9504139962807976</v>
+        <v>0.97511944977862963</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -25609,19 +25600,19 @@
         <v>394</v>
       </c>
       <c r="C24">
-        <v>60.29340062591924</v>
+        <v>53.236591595167631</v>
       </c>
       <c r="D24">
-        <v>-1.2719451172071998</v>
+        <v>-3.0503636016203881</v>
       </c>
       <c r="F24" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G24">
-        <v>60.29340062591924</v>
+        <v>53.236591595167631</v>
       </c>
       <c r="H24">
-        <v>-1.2719451172071998</v>
+        <v>-3.0503636016203881</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -25629,19 +25620,19 @@
         <v>395</v>
       </c>
       <c r="C25">
-        <v>51.440498299145609</v>
+        <v>50.818035638860259</v>
       </c>
       <c r="D25">
-        <v>0.71615754360028872</v>
+        <v>-1.194439480272105</v>
       </c>
       <c r="F25" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G25">
-        <v>51.440498299145609</v>
+        <v>50.818035638860259</v>
       </c>
       <c r="H25">
-        <v>0.71615754360028872</v>
+        <v>-1.194439480272105</v>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -25649,19 +25640,19 @@
         <v>396</v>
       </c>
       <c r="C26">
-        <v>53.236591595167631</v>
+        <v>55.146475961917993</v>
       </c>
       <c r="D26">
-        <v>-3.0503636016203881</v>
+        <v>-1.5404269162550226</v>
       </c>
       <c r="F26" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G26">
-        <v>53.236591595167631</v>
+        <v>55.146475961917993</v>
       </c>
       <c r="H26">
-        <v>-3.0503636016203881</v>
+        <v>-1.5404269162550226</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -25669,19 +25660,19 @@
         <v>397</v>
       </c>
       <c r="C27">
-        <v>55.146475961917993</v>
+        <v>51.09844688040387</v>
       </c>
       <c r="D27">
-        <v>-1.5404269162550226</v>
+        <v>1.1448358124246545</v>
       </c>
       <c r="F27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="G27">
-        <v>55.146475961917993</v>
+        <v>51.09844688040387</v>
       </c>
       <c r="H27">
-        <v>-1.5404269162550226</v>
+        <v>1.1448358124246545</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -25689,19 +25680,19 @@
         <v>398</v>
       </c>
       <c r="C28">
-        <v>54.369942938278029</v>
+        <v>51.129886219814694</v>
       </c>
       <c r="D28">
-        <v>-6.4252938772591932</v>
+        <v>-2.0707206800269599E-2</v>
       </c>
       <c r="F28" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G28">
-        <v>54.369942938278029</v>
+        <v>51.129886219814694</v>
       </c>
       <c r="H28">
-        <v>-6.4252938772591932</v>
+        <v>-2.0707206800269599E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -25709,19 +25700,19 @@
         <v>399</v>
       </c>
       <c r="C29">
-        <v>51.129886219814694</v>
+        <v>51.350285918353343</v>
       </c>
       <c r="D29">
-        <v>-2.0707206800269599E-2</v>
+        <v>-0.70217833785863937</v>
       </c>
       <c r="F29" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G29">
-        <v>51.129886219814694</v>
+        <v>51.350285918353343</v>
       </c>
       <c r="H29">
-        <v>-2.0707206800269599E-2</v>
+        <v>-0.70217833785863937</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -25729,19 +25720,19 @@
         <v>400</v>
       </c>
       <c r="C30">
-        <v>51.350285918353343</v>
+        <v>53.955760976359223</v>
       </c>
       <c r="D30">
-        <v>-0.70217833785863937</v>
+        <v>-1.3255014442970323</v>
       </c>
       <c r="F30" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G30">
-        <v>51.350285918353343</v>
+        <v>53.955760976359223</v>
       </c>
       <c r="H30">
-        <v>-0.70217833785863937</v>
+        <v>-1.3255014442970323</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -25749,19 +25740,19 @@
         <v>401</v>
       </c>
       <c r="C31">
-        <v>53.955760976359223</v>
+        <v>52.998038908826409</v>
       </c>
       <c r="D31">
-        <v>-1.3255014442970323</v>
+        <v>-1.4210946637382096</v>
       </c>
       <c r="F31" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G31">
-        <v>53.955760976359223</v>
+        <v>52.998038908826409</v>
       </c>
       <c r="H31">
-        <v>-1.3255014442970323</v>
+        <v>-1.4210946637382096</v>
       </c>
     </row>
     <row r="32" spans="2:8">
@@ -25769,19 +25760,19 @@
         <v>402</v>
       </c>
       <c r="C32">
-        <v>52.998038908826409</v>
+        <v>52.09871854510186</v>
       </c>
       <c r="D32">
-        <v>-1.4210946637382096</v>
+        <v>-4.2164210245146929</v>
       </c>
       <c r="F32" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G32">
-        <v>52.998038908826409</v>
+        <v>52.09871854510186</v>
       </c>
       <c r="H32">
-        <v>-1.4210946637382096</v>
+        <v>-4.2164210245146929</v>
       </c>
     </row>
     <row r="33" spans="2:8">
@@ -25789,16 +25780,16 @@
         <v>403</v>
       </c>
       <c r="C33">
-        <v>52.09871854510186</v>
+        <v>50.749737999515048</v>
       </c>
       <c r="D33">
         <v>-4.2164210245146929</v>
       </c>
       <c r="F33" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G33">
-        <v>52.09871854510186</v>
+        <v>50.749737999515048</v>
       </c>
       <c r="H33">
         <v>-4.2164210245146929</v>
@@ -25809,19 +25800,19 @@
         <v>404</v>
       </c>
       <c r="C34">
-        <v>50.749737999515048</v>
+        <v>51.114817127268097</v>
       </c>
       <c r="D34">
-        <v>-4.2164210245146929</v>
+        <v>-2.9603260086483649</v>
       </c>
       <c r="F34" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G34">
-        <v>50.749737999515048</v>
+        <v>51.114817127268097</v>
       </c>
       <c r="H34">
-        <v>-4.2164210245146929</v>
+        <v>-2.9603260086483649</v>
       </c>
     </row>
     <row r="35" spans="2:8">
@@ -25829,19 +25820,19 @@
         <v>405</v>
       </c>
       <c r="C35">
-        <v>51.114817127268097</v>
+        <v>53.333247860859522</v>
       </c>
       <c r="D35">
-        <v>-2.9603260086483649</v>
+        <v>-2.4505764869547897</v>
       </c>
       <c r="F35" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G35">
-        <v>51.114817127268097</v>
+        <v>53.333247860859522</v>
       </c>
       <c r="H35">
-        <v>-2.9603260086483649</v>
+        <v>-2.4505764869547897</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -25849,19 +25840,19 @@
         <v>406</v>
       </c>
       <c r="C36">
-        <v>53.333247860859522</v>
+        <v>52.433140350023393</v>
       </c>
       <c r="D36">
-        <v>-2.4505764869547897</v>
+        <v>-3.359738834754292</v>
       </c>
       <c r="F36" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G36">
-        <v>53.333247860859522</v>
+        <v>52.433140350023393</v>
       </c>
       <c r="H36">
-        <v>-2.4505764869547897</v>
+        <v>-3.359738834754292</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -25869,19 +25860,19 @@
         <v>407</v>
       </c>
       <c r="C37">
-        <v>52.433140350023393</v>
+        <v>54.847484775151209</v>
       </c>
       <c r="D37">
-        <v>-3.359738834754292</v>
+        <v>-2.9853580781416813</v>
       </c>
       <c r="F37" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G37">
-        <v>52.433140350023393</v>
+        <v>54.847484775151209</v>
       </c>
       <c r="H37">
-        <v>-3.359738834754292</v>
+        <v>-2.9853580781416813</v>
       </c>
     </row>
     <row r="38" spans="2:8">
@@ -25889,19 +25880,19 @@
         <v>408</v>
       </c>
       <c r="C38">
-        <v>54.847484775151209</v>
+        <v>55.458182669785081</v>
       </c>
       <c r="D38">
-        <v>-2.9853580781416813</v>
+        <v>-2.574279120717724</v>
       </c>
       <c r="F38" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G38">
-        <v>54.847484775151209</v>
+        <v>55.458182669785081</v>
       </c>
       <c r="H38">
-        <v>-2.9853580781416813</v>
+        <v>-2.574279120717724</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -25909,19 +25900,19 @@
         <v>409</v>
       </c>
       <c r="C39">
-        <v>55.458182669785081</v>
+        <v>57.312520717407011</v>
       </c>
       <c r="D39">
-        <v>-2.574279120717724</v>
+        <v>-2.9347207170634784</v>
       </c>
       <c r="F39" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G39">
-        <v>55.458182669785081</v>
+        <v>57.312520717407011</v>
       </c>
       <c r="H39">
-        <v>-2.574279120717724</v>
+        <v>-2.9347207170634784</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -25929,19 +25920,19 @@
         <v>410</v>
       </c>
       <c r="C40">
-        <v>57.312520717407011</v>
+        <v>58.467822508750082</v>
       </c>
       <c r="D40">
-        <v>-2.9347207170634784</v>
+        <v>-3.4345900866775727</v>
       </c>
       <c r="F40" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G40">
-        <v>57.312520717407011</v>
+        <v>58.467822508750082</v>
       </c>
       <c r="H40">
-        <v>-2.9347207170634784</v>
+        <v>-3.4345900866775727</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -25949,19 +25940,19 @@
         <v>411</v>
       </c>
       <c r="C41">
-        <v>58.467822508750082</v>
+        <v>58.016138840172239</v>
       </c>
       <c r="D41">
-        <v>-3.4345900866775727</v>
+        <v>-4.3385965029843447</v>
       </c>
       <c r="F41" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G41">
-        <v>58.467822508750082</v>
+        <v>58.016138840172239</v>
       </c>
       <c r="H41">
-        <v>-3.4345900866775727</v>
+        <v>-4.3385965029843447</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -25969,19 +25960,19 @@
         <v>412</v>
       </c>
       <c r="C42">
-        <v>58.016138840172239</v>
+        <v>57.494640727449102</v>
       </c>
       <c r="D42">
-        <v>-4.3385965029843447</v>
+        <v>-6.3129157950970578</v>
       </c>
       <c r="F42" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G42">
-        <v>58.016138840172239</v>
+        <v>57.494640727449102</v>
       </c>
       <c r="H42">
-        <v>-4.3385965029843447</v>
+        <v>-6.3129157950970578</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -25989,19 +25980,19 @@
         <v>413</v>
       </c>
       <c r="C43">
-        <v>57.494640727449102</v>
+        <v>57.44058733138791</v>
       </c>
       <c r="D43">
-        <v>-6.3129157950970578</v>
+        <v>-7.1619929137138953</v>
       </c>
       <c r="F43" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G43">
-        <v>57.494640727449102</v>
+        <v>57.44058733138791</v>
       </c>
       <c r="H43">
-        <v>-6.3129157950970578</v>
+        <v>-7.1619929137138953</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -26009,19 +26000,19 @@
         <v>414</v>
       </c>
       <c r="C44">
-        <v>57.44058733138791</v>
+        <v>58.307484194835531</v>
       </c>
       <c r="D44">
-        <v>-7.1619929137138953</v>
+        <v>-6.3967206557211638</v>
       </c>
       <c r="F44" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G44">
-        <v>57.44058733138791</v>
+        <v>58.307484194835531</v>
       </c>
       <c r="H44">
-        <v>-7.1619929137138953</v>
+        <v>-6.3967206557211638</v>
       </c>
     </row>
     <row r="45" spans="2:8">
@@ -26029,19 +26020,19 @@
         <v>415</v>
       </c>
       <c r="C45">
-        <v>58.307484194835531</v>
+        <v>54.482513890704034</v>
       </c>
       <c r="D45">
-        <v>-6.3967206557211638</v>
+        <v>-6.2256037810741063</v>
       </c>
       <c r="F45" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G45">
-        <v>58.307484194835531</v>
+        <v>54.482513890704034</v>
       </c>
       <c r="H45">
-        <v>-6.3967206557211638</v>
+        <v>-6.2256037810741063</v>
       </c>
     </row>
     <row r="46" spans="2:8">
@@ -26049,19 +26040,19 @@
         <v>416</v>
       </c>
       <c r="C46">
-        <v>54.482513890704034</v>
+        <v>54.347019454413221</v>
       </c>
       <c r="D46">
-        <v>-6.2256037810741063</v>
+        <v>-7.7105789754852996</v>
       </c>
       <c r="F46" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G46">
-        <v>54.482513890704034</v>
+        <v>54.347019454413221</v>
       </c>
       <c r="H46">
-        <v>-6.2256037810741063</v>
+        <v>-7.7105789754852996</v>
       </c>
     </row>
     <row r="47" spans="2:8">
@@ -26069,19 +26060,19 @@
         <v>417</v>
       </c>
       <c r="C47">
-        <v>54.347019454413221</v>
+        <v>55.696000000000033</v>
       </c>
       <c r="D47">
-        <v>-7.7105789754852996</v>
+        <v>-5.6140842049029356</v>
       </c>
       <c r="F47" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G47">
-        <v>54.347019454413221</v>
+        <v>55.696000000000033</v>
       </c>
       <c r="H47">
-        <v>-7.7105789754852996</v>
+        <v>-5.6140842049029356</v>
       </c>
     </row>
     <row r="48" spans="2:8">
@@ -26089,19 +26080,19 @@
         <v>418</v>
       </c>
       <c r="C48">
-        <v>55.696000000000033</v>
+        <v>55.421901011994777</v>
       </c>
       <c r="D48">
-        <v>-5.6140842049029356</v>
+        <v>-4.3621456969842614</v>
       </c>
       <c r="F48" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G48">
-        <v>55.696000000000033</v>
+        <v>55.421901011994777</v>
       </c>
       <c r="H48">
-        <v>-5.6140842049029356</v>
+        <v>-4.3621456969842614</v>
       </c>
     </row>
     <row r="49" spans="2:8">
@@ -26109,19 +26100,19 @@
         <v>419</v>
       </c>
       <c r="C49">
-        <v>55.421901011994777</v>
+        <v>54.504353765138951</v>
       </c>
       <c r="D49">
-        <v>-4.3621456969842614</v>
+        <v>-2.344980354574</v>
       </c>
       <c r="F49" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G49">
-        <v>55.421901011994777</v>
+        <v>54.504353765138951</v>
       </c>
       <c r="H49">
-        <v>-4.3621456969842614</v>
+        <v>-2.344980354574</v>
       </c>
     </row>
     <row r="50" spans="2:8">
@@ -26129,19 +26120,19 @@
         <v>420</v>
       </c>
       <c r="C50">
-        <v>54.504353765138951</v>
+        <v>53.438585044068283</v>
       </c>
       <c r="D50">
-        <v>-2.344980354574</v>
+        <v>-2.4377382045774927</v>
       </c>
       <c r="F50" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G50">
-        <v>54.504353765138951</v>
+        <v>53.438585044068283</v>
       </c>
       <c r="H50">
-        <v>-2.344980354574</v>
+        <v>-2.4377382045774927</v>
       </c>
     </row>
     <row r="51" spans="2:8">
@@ -26149,19 +26140,19 @@
         <v>421</v>
       </c>
       <c r="C51">
-        <v>53.438585044068283</v>
+        <v>52.556800545334717</v>
       </c>
       <c r="D51">
-        <v>-2.4377382045774927</v>
+        <v>-3.3381547327896679</v>
       </c>
       <c r="F51" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G51">
-        <v>53.438585044068283</v>
+        <v>52.556800545334717</v>
       </c>
       <c r="H51">
-        <v>-2.4377382045774927</v>
+        <v>-3.3381547327896679</v>
       </c>
     </row>
     <row r="52" spans="2:8">
@@ -26169,19 +26160,19 @@
         <v>422</v>
       </c>
       <c r="C52">
-        <v>52.556800545334717</v>
+        <v>53.380852119426265</v>
       </c>
       <c r="D52">
-        <v>-3.3381547327896679</v>
+        <v>-1.4065792377621205</v>
       </c>
       <c r="F52" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G52">
-        <v>52.556800545334717</v>
+        <v>53.380852119426265</v>
       </c>
       <c r="H52">
-        <v>-3.3381547327896679</v>
+        <v>-1.4065792377621205</v>
       </c>
     </row>
     <row r="53" spans="2:8">
@@ -26189,19 +26180,19 @@
         <v>423</v>
       </c>
       <c r="C53">
-        <v>53.380852119426265</v>
+        <v>50.869607144808178</v>
       </c>
       <c r="D53">
-        <v>-1.4065792377621205</v>
+        <v>-0.14504652877770399</v>
       </c>
       <c r="F53" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G53">
-        <v>53.380852119426265</v>
+        <v>50.869607144808178</v>
       </c>
       <c r="H53">
-        <v>-1.4065792377621205</v>
+        <v>-0.14504652877770399</v>
       </c>
     </row>
     <row r="54" spans="2:8">
@@ -26209,19 +26200,19 @@
         <v>424</v>
       </c>
       <c r="C54">
-        <v>50.869607144808178</v>
+        <v>51.325096113838967</v>
       </c>
       <c r="D54">
-        <v>-0.14504652877770399</v>
+        <v>-0.44685731418639452</v>
       </c>
       <c r="F54" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G54">
-        <v>50.869607144808178</v>
+        <v>51.325096113838967</v>
       </c>
       <c r="H54">
-        <v>-0.14504652877770399</v>
+        <v>-0.44685731418639452</v>
       </c>
     </row>
     <row r="55" spans="2:8">
@@ -26229,19 +26220,19 @@
         <v>425</v>
       </c>
       <c r="C55">
-        <v>51.325096113838967</v>
+        <v>52.09871854510186</v>
       </c>
       <c r="D55">
-        <v>-0.44685731418639452</v>
+        <v>-4.2164210245146929</v>
       </c>
       <c r="F55" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G55">
-        <v>51.325096113838967</v>
+        <v>52.09871854510186</v>
       </c>
       <c r="H55">
-        <v>-0.44685731418639452</v>
+        <v>-4.2164210245146929</v>
       </c>
     </row>
     <row r="56" spans="2:8">
@@ -26249,19 +26240,19 @@
         <v>426</v>
       </c>
       <c r="C56">
-        <v>52.09871854510186</v>
+        <v>50.691067132763997</v>
       </c>
       <c r="D56">
-        <v>-4.2164210245146929</v>
+        <v>-4.2626597113208051</v>
       </c>
       <c r="F56" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G56">
-        <v>52.09871854510186</v>
+        <v>50.691067132763997</v>
       </c>
       <c r="H56">
-        <v>-4.2164210245146929</v>
+        <v>-4.2626597113208051</v>
       </c>
     </row>
     <row r="57" spans="2:8">
@@ -26269,19 +26260,19 @@
         <v>427</v>
       </c>
       <c r="C57">
-        <v>50.691067132763997</v>
+        <v>51.199398181377319</v>
       </c>
       <c r="D57">
-        <v>-4.2626597113208051</v>
+        <v>-2.818757844126452</v>
       </c>
       <c r="F57" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G57">
-        <v>50.691067132763997</v>
+        <v>51.199398181377319</v>
       </c>
       <c r="H57">
-        <v>-4.2626597113208051</v>
+        <v>-2.818757844126452</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -26289,19 +26280,19 @@
         <v>428</v>
       </c>
       <c r="C58">
-        <v>51.199398181377319</v>
+        <v>58.392236623602678</v>
       </c>
       <c r="D58">
-        <v>-2.818757844126452</v>
+        <v>-4.0597322285057844</v>
       </c>
       <c r="F58" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G58">
-        <v>51.199398181377319</v>
+        <v>58.392236623602678</v>
       </c>
       <c r="H58">
-        <v>-2.818757844126452</v>
+        <v>-4.0597322285057844</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -26309,19 +26300,19 @@
         <v>429</v>
       </c>
       <c r="C59">
-        <v>58.392236623602678</v>
+        <v>58.98740565519239</v>
       </c>
       <c r="D59">
-        <v>-4.0597322285057844</v>
+        <v>-3.0065803762848389</v>
       </c>
       <c r="F59" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="G59">
-        <v>58.392236623602678</v>
+        <v>58.98740565519239</v>
       </c>
       <c r="H59">
-        <v>-4.0597322285057844</v>
+        <v>-3.0065803762848389</v>
       </c>
     </row>
     <row r="60" spans="2:8">
@@ -26329,19 +26320,19 @@
         <v>430</v>
       </c>
       <c r="C60">
-        <v>58.98740565519239</v>
+        <v>58.128655423966627</v>
       </c>
       <c r="D60">
-        <v>-3.0065803762848389</v>
+        <v>-6.5135735759051263</v>
       </c>
       <c r="F60" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G60">
-        <v>58.98740565519239</v>
+        <v>58.128655423966627</v>
       </c>
       <c r="H60">
-        <v>-3.0065803762848389</v>
+        <v>-6.5135735759051263</v>
       </c>
     </row>
     <row r="61" spans="2:8">
@@ -26349,19 +26340,19 @@
         <v>431</v>
       </c>
       <c r="C61">
-        <v>58.128655423966627</v>
+        <v>57.494640727449102</v>
       </c>
       <c r="D61">
-        <v>-6.5135735759051263</v>
+        <v>-6.3129157950970578</v>
       </c>
       <c r="F61" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G61">
-        <v>58.128655423966627</v>
+        <v>57.494640727449102</v>
       </c>
       <c r="H61">
-        <v>-6.5135735759051263</v>
+        <v>-6.3129157950970578</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -26369,19 +26360,19 @@
         <v>432</v>
       </c>
       <c r="C62">
-        <v>57.494640727449102</v>
+        <v>54.401332652035698</v>
       </c>
       <c r="D62">
-        <v>-6.3129157950970578</v>
+        <v>-6.947513321698696</v>
       </c>
       <c r="F62" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G62">
-        <v>57.494640727449102</v>
+        <v>54.401332652035698</v>
       </c>
       <c r="H62">
-        <v>-6.3129157950970578</v>
+        <v>-6.947513321698696</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -26389,19 +26380,19 @@
         <v>433</v>
       </c>
       <c r="C63">
-        <v>54.401332652035698</v>
+        <v>54.960422195930917</v>
       </c>
       <c r="D63">
-        <v>-6.947513321698696</v>
+        <v>-6.1977434177953645</v>
       </c>
       <c r="F63" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G63">
-        <v>54.401332652035698</v>
+        <v>54.960422195930917</v>
       </c>
       <c r="H63">
-        <v>-6.947513321698696</v>
+        <v>-6.1977434177953645</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -26409,19 +26400,19 @@
         <v>434</v>
       </c>
       <c r="C64">
-        <v>54.960422195930917</v>
+        <v>57.766041264728578</v>
       </c>
       <c r="D64">
-        <v>-6.1977434177953645</v>
+        <v>-4.5483891016678735</v>
       </c>
       <c r="F64" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G64">
-        <v>54.960422195930917</v>
+        <v>57.766041264728578</v>
       </c>
       <c r="H64">
-        <v>-6.1977434177953645</v>
+        <v>-4.5483891016678735</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -26429,19 +26420,19 @@
         <v>435</v>
       </c>
       <c r="C65">
-        <v>57.766041264728578</v>
+        <v>56.781267997554025</v>
       </c>
       <c r="D65">
-        <v>-4.5483891016678735</v>
+        <v>-4.5306651620602842</v>
       </c>
       <c r="F65" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G65">
-        <v>57.766041264728578</v>
+        <v>56.781267997554025</v>
       </c>
       <c r="H65">
-        <v>-4.5483891016678735</v>
+        <v>-4.5306651620602842</v>
       </c>
     </row>
     <row r="66" spans="2:8">
@@ -26449,19 +26440,19 @@
         <v>436</v>
       </c>
       <c r="C66">
-        <v>56.781267997554025</v>
+        <v>57.458500887309789</v>
       </c>
       <c r="D66">
-        <v>-4.5306651620602842</v>
+        <v>-2.7079036356420234</v>
       </c>
       <c r="F66" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G66">
-        <v>56.781267997554025</v>
+        <v>57.458500887309789</v>
       </c>
       <c r="H66">
-        <v>-4.5306651620602842</v>
+        <v>-2.7079036356420234</v>
       </c>
     </row>
     <row r="67" spans="2:8">
@@ -26469,19 +26460,19 @@
         <v>437</v>
       </c>
       <c r="C67">
-        <v>57.458500887309789</v>
+        <v>56.910569430643221</v>
       </c>
       <c r="D67">
-        <v>-2.7079036356420234</v>
+        <v>-3.288940859602596</v>
       </c>
       <c r="F67" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G67">
-        <v>57.458500887309789</v>
+        <v>56.910569430643221</v>
       </c>
       <c r="H67">
-        <v>-2.7079036356420234</v>
+        <v>-3.288940859602596</v>
       </c>
     </row>
     <row r="68" spans="2:8">
@@ -26489,19 +26480,19 @@
         <v>438</v>
       </c>
       <c r="C68">
-        <v>56.910569430643221</v>
+        <v>55.377291546710254</v>
       </c>
       <c r="D68">
-        <v>-3.288940859602596</v>
+        <v>-3.4817580307726108</v>
       </c>
       <c r="F68" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G68">
-        <v>56.910569430643221</v>
+        <v>55.377291546710254</v>
       </c>
       <c r="H68">
-        <v>-3.288940859602596</v>
+        <v>-3.4817580307726108</v>
       </c>
     </row>
     <row r="69" spans="2:8">
@@ -26509,19 +26500,19 @@
         <v>439</v>
       </c>
       <c r="C69">
-        <v>55.377291546710254</v>
+        <v>54.796679636275485</v>
       </c>
       <c r="D69">
-        <v>-3.4817580307726108</v>
+        <v>-1.4210946637382096</v>
       </c>
       <c r="F69" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G69">
-        <v>55.377291546710254</v>
+        <v>54.796679636275485</v>
       </c>
       <c r="H69">
-        <v>-3.4817580307726108</v>
+        <v>-1.4210946637382096</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -26529,19 +26520,19 @@
         <v>440</v>
       </c>
       <c r="C70">
-        <v>54.796679636275485</v>
+        <v>51.814449536938859</v>
       </c>
       <c r="D70">
-        <v>-1.4210946637382096</v>
+        <v>2.0216393884377029</v>
       </c>
       <c r="F70" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G70">
-        <v>54.796679636275485</v>
+        <v>51.814449536938859</v>
       </c>
       <c r="H70">
-        <v>-1.4210946637382096</v>
+        <v>2.0216393884377029</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -26549,19 +26540,19 @@
         <v>441</v>
       </c>
       <c r="C71">
-        <v>51.814449536938859</v>
+        <v>50.195574434657651</v>
       </c>
       <c r="D71">
-        <v>2.0216393884377029</v>
+        <v>-0.18240086741005429</v>
       </c>
       <c r="F71" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G71">
-        <v>51.814449536938859</v>
+        <v>50.195574434657651</v>
       </c>
       <c r="H71">
-        <v>2.0216393884377029</v>
+        <v>-0.18240086741005429</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -26569,19 +26560,19 @@
         <v>442</v>
       </c>
       <c r="C72">
-        <v>50.195574434657651</v>
+        <v>49.956546129419536</v>
       </c>
       <c r="D72">
-        <v>-0.18240086741005429</v>
+        <v>-2.5883070368014987</v>
       </c>
       <c r="F72" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G72">
-        <v>50.195574434657651</v>
+        <v>49.956546129419536</v>
       </c>
       <c r="H72">
-        <v>-0.18240086741005429</v>
+        <v>-2.5883070368014987</v>
       </c>
     </row>
     <row r="73" spans="2:8">
@@ -26589,19 +26580,19 @@
         <v>443</v>
       </c>
       <c r="C73">
-        <v>49.956546129419536</v>
+        <v>52.37468165037906</v>
       </c>
       <c r="D73">
-        <v>-2.5883070368014987</v>
+        <v>-5.5885110580996162</v>
       </c>
       <c r="F73" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G73">
-        <v>49.956546129419536</v>
+        <v>52.37468165037906</v>
       </c>
       <c r="H73">
-        <v>-2.5883070368014987</v>
+        <v>-5.5885110580996162</v>
       </c>
     </row>
     <row r="74" spans="2:8">
@@ -26609,19 +26600,19 @@
         <v>444</v>
       </c>
       <c r="C74">
-        <v>52.37468165037906</v>
+        <v>54.140844211473805</v>
       </c>
       <c r="D74">
-        <v>-5.5885110580996162</v>
+        <v>-5.2337592076417785</v>
       </c>
       <c r="F74" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G74">
-        <v>52.37468165037906</v>
+        <v>54.140844211473805</v>
       </c>
       <c r="H74">
-        <v>-5.5885110580996162</v>
+        <v>-5.2337592076417785</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -26629,19 +26620,19 @@
         <v>445</v>
       </c>
       <c r="C75">
-        <v>54.140844211473805</v>
+        <v>50.721999039307683</v>
       </c>
       <c r="D75">
-        <v>-5.2337592076417785</v>
+        <v>-5.2714029336588215</v>
       </c>
       <c r="F75" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G75">
-        <v>54.140844211473805</v>
+        <v>50.721999039307683</v>
       </c>
       <c r="H75">
-        <v>-5.2337592076417785</v>
+        <v>-5.2714029336588215</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -26649,19 +26640,19 @@
         <v>446</v>
       </c>
       <c r="C76">
-        <v>50.721999039307683</v>
+        <v>50.425397773312447</v>
       </c>
       <c r="D76">
-        <v>-5.2714029336588215</v>
+        <v>-7.2303393756033012</v>
       </c>
       <c r="F76" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G76">
-        <v>50.721999039307683</v>
+        <v>50.425397773312447</v>
       </c>
       <c r="H76">
-        <v>-5.2714029336588215</v>
+        <v>-7.2303393756033012</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -26669,19 +26660,19 @@
         <v>447</v>
       </c>
       <c r="C77">
-        <v>50.425397773312447</v>
+        <v>49.091721092564342</v>
       </c>
       <c r="D77">
-        <v>-7.2303393756033012</v>
+        <v>-7.9537693299676819</v>
       </c>
       <c r="F77" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G77">
-        <v>50.425397773312447</v>
+        <v>49.091721092564342</v>
       </c>
       <c r="H77">
-        <v>-7.2303393756033012</v>
+        <v>-7.9537693299676819</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -26689,19 +26680,19 @@
         <v>448</v>
       </c>
       <c r="C78">
-        <v>49.091721092564342</v>
+        <v>49.292063923918882</v>
       </c>
       <c r="D78">
-        <v>-7.9537693299676819</v>
+        <v>-5.5297378779879649</v>
       </c>
       <c r="F78" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G78">
-        <v>49.091721092564342</v>
+        <v>49.292063923918882</v>
       </c>
       <c r="H78">
-        <v>-7.9537693299676819</v>
+        <v>-5.5297378779879649</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -26709,19 +26700,19 @@
         <v>449</v>
       </c>
       <c r="C79">
-        <v>49.292063923918882</v>
+        <v>56.566432276821693</v>
       </c>
       <c r="D79">
-        <v>-5.5297378779879649</v>
+        <v>-8.1059715229376064</v>
       </c>
       <c r="F79" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G79">
-        <v>49.292063923918882</v>
+        <v>56.566432276821693</v>
       </c>
       <c r="H79">
-        <v>-5.5297378779879649</v>
+        <v>-8.1059715229376064</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -26729,19 +26720,19 @@
         <v>450</v>
       </c>
       <c r="C80">
-        <v>56.566432276821693</v>
+        <v>55.940255849688462</v>
       </c>
       <c r="D80">
-        <v>-8.1059715229376064</v>
+        <v>-6.4562660095073063</v>
       </c>
       <c r="F80" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G80">
-        <v>56.566432276821693</v>
+        <v>55.940255849688462</v>
       </c>
       <c r="H80">
-        <v>-8.1059715229376064</v>
+        <v>-6.4562660095073063</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -26749,19 +26740,19 @@
         <v>451</v>
       </c>
       <c r="C81">
-        <v>55.940255849688462</v>
+        <v>58.19770237393876</v>
       </c>
       <c r="D81">
-        <v>-6.4562660095073063</v>
+        <v>-5.9103899512457856</v>
       </c>
       <c r="F81" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G81">
-        <v>55.940255849688462</v>
+        <v>58.19770237393876</v>
       </c>
       <c r="H81">
-        <v>-6.4562660095073063</v>
+        <v>-5.9103899512457856</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -26769,19 +26760,19 @@
         <v>452</v>
       </c>
       <c r="C82">
-        <v>58.19770237393876</v>
+        <v>56.339117381667485</v>
       </c>
       <c r="D82">
-        <v>-5.9103899512457856</v>
+        <v>-2.4177325211769389</v>
       </c>
       <c r="F82" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G82">
-        <v>58.19770237393876</v>
+        <v>56.339117381667485</v>
       </c>
       <c r="H82">
-        <v>-5.9103899512457856</v>
+        <v>-2.4177325211769389</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -26789,19 +26780,19 @@
         <v>453</v>
       </c>
       <c r="C83">
-        <v>56.339117381667485</v>
+        <v>56.59770164798509</v>
       </c>
       <c r="D83">
-        <v>-2.4177325211769389</v>
+        <v>-5.0823735586540417</v>
       </c>
       <c r="F83" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G83">
-        <v>56.339117381667485</v>
+        <v>56.59770164798509</v>
       </c>
       <c r="H83">
-        <v>-2.4177325211769389</v>
+        <v>-5.0823735586540417</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -26809,19 +26800,19 @@
         <v>454</v>
       </c>
       <c r="C84">
-        <v>56.59770164798509</v>
+        <v>57.707870547714414</v>
       </c>
       <c r="D84">
-        <v>-5.0823735586540417</v>
+        <v>-3.2423068373323534</v>
       </c>
       <c r="F84" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G84">
-        <v>56.59770164798509</v>
+        <v>57.707870547714414</v>
       </c>
       <c r="H84">
-        <v>-5.0823735586540417</v>
+        <v>-3.2423068373323534</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -26829,19 +26820,19 @@
         <v>455</v>
       </c>
       <c r="C85">
-        <v>57.707870547714414</v>
+        <v>59.055525157654493</v>
       </c>
       <c r="D85">
-        <v>-3.2423068373323534</v>
+        <v>-14.047209238692638</v>
       </c>
       <c r="F85" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G85">
-        <v>57.707870547714414</v>
+        <v>59.055525157654493</v>
       </c>
       <c r="H85">
-        <v>-3.2423068373323534</v>
+        <v>-14.047209238692638</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -26849,19 +26840,19 @@
         <v>456</v>
       </c>
       <c r="C86">
-        <v>59.055525157654493</v>
+        <v>57.546880838979405</v>
       </c>
       <c r="D86">
-        <v>-14.047209238692638</v>
+        <v>-13.964068873818908</v>
       </c>
       <c r="F86" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G86">
-        <v>59.055525157654493</v>
+        <v>57.546880838979405</v>
       </c>
       <c r="H86">
-        <v>-14.047209238692638</v>
+        <v>-13.964068873818908</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -26869,19 +26860,19 @@
         <v>457</v>
       </c>
       <c r="C87">
-        <v>57.546880838979405</v>
+        <v>57.754129727894053</v>
       </c>
       <c r="D87">
-        <v>-13.964068873818908</v>
+        <v>-9.3469421599286928</v>
       </c>
       <c r="F87" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G87">
-        <v>57.546880838979405</v>
+        <v>57.754129727894053</v>
       </c>
       <c r="H87">
-        <v>-13.964068873818908</v>
+        <v>-9.3469421599286928</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -26889,19 +26880,19 @@
         <v>458</v>
       </c>
       <c r="C88">
-        <v>57.754129727894053</v>
+        <v>58.344777922872559</v>
       </c>
       <c r="D88">
-        <v>-9.3469421599286928</v>
+        <v>-7.7698883628779383</v>
       </c>
       <c r="F88" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G88">
-        <v>57.754129727894053</v>
+        <v>58.344777922872559</v>
       </c>
       <c r="H88">
-        <v>-9.3469421599286928</v>
+        <v>-7.7698883628779383</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -26909,19 +26900,19 @@
         <v>459</v>
       </c>
       <c r="C89">
-        <v>58.344777922872559</v>
+        <v>59.774795563720602</v>
       </c>
       <c r="D89">
-        <v>-7.7698883628779383</v>
+        <v>-7.9600617653293408</v>
       </c>
       <c r="F89" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G89">
-        <v>58.344777922872559</v>
+        <v>59.774795563720602</v>
       </c>
       <c r="H89">
-        <v>-7.7698883628779383</v>
+        <v>-7.9600617653293408</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -26929,19 +26920,19 @@
         <v>460</v>
       </c>
       <c r="C90">
-        <v>59.774795563720602</v>
+        <v>59.538509083966986</v>
       </c>
       <c r="D90">
-        <v>-7.9600617653293408</v>
+        <v>-5.5825490878430823</v>
       </c>
       <c r="F90" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G90">
-        <v>59.774795563720602</v>
+        <v>59.538509083966986</v>
       </c>
       <c r="H90">
-        <v>-7.9600617653293408</v>
+        <v>-5.5825490878430823</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -26949,19 +26940,19 @@
         <v>461</v>
       </c>
       <c r="C91">
-        <v>59.538509083966986</v>
+        <v>60.051105327929811</v>
       </c>
       <c r="D91">
-        <v>-5.5825490878430823</v>
+        <v>-3.6784526581282702</v>
       </c>
       <c r="F91" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G91">
-        <v>59.538509083966986</v>
+        <v>60.051105327929811</v>
       </c>
       <c r="H91">
-        <v>-5.5825490878430823</v>
+        <v>-3.6784526581282702</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -26969,19 +26960,19 @@
         <v>462</v>
       </c>
       <c r="C92">
-        <v>60.051105327929811</v>
+        <v>62.127353904250043</v>
       </c>
       <c r="D92">
-        <v>-3.6784526581282702</v>
+        <v>-3.106577828984713</v>
       </c>
       <c r="F92" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G92">
-        <v>60.051105327929811</v>
+        <v>62.127353904250043</v>
       </c>
       <c r="H92">
-        <v>-3.6784526581282702</v>
+        <v>-3.106577828984713</v>
       </c>
     </row>
     <row r="93" spans="2:8">
@@ -26989,19 +26980,19 @@
         <v>463</v>
       </c>
       <c r="C93">
-        <v>62.127353904250043</v>
+        <v>60.61727754533127</v>
       </c>
       <c r="D93">
-        <v>-3.106577828984713</v>
+        <v>-1.8149132865558519</v>
       </c>
       <c r="F93" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G93">
-        <v>62.127353904250043</v>
+        <v>60.61727754533127</v>
       </c>
       <c r="H93">
-        <v>-3.106577828984713</v>
+        <v>-1.8149132865558519</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -27009,19 +27000,19 @@
         <v>464</v>
       </c>
       <c r="C94">
-        <v>60.61727754533127</v>
+        <v>61.762336685714295</v>
       </c>
       <c r="D94">
-        <v>-1.8149132865558519</v>
+        <v>0.40481491367400008</v>
       </c>
       <c r="F94" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G94">
-        <v>60.61727754533127</v>
+        <v>61.762336685714295</v>
       </c>
       <c r="H94">
-        <v>-1.8149132865558519</v>
+        <v>0.40481491367400008</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -27029,19 +27020,19 @@
         <v>465</v>
       </c>
       <c r="C95">
-        <v>61.762336685714295</v>
+        <v>60.15808988404617</v>
       </c>
       <c r="D95">
-        <v>0.40481491367400008</v>
+        <v>1.9118952552866653</v>
       </c>
       <c r="F95" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G95">
-        <v>61.762336685714295</v>
+        <v>60.15808988404617</v>
       </c>
       <c r="H95">
-        <v>0.40481491367400008</v>
+        <v>1.9118952552866653</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -27049,19 +27040,19 @@
         <v>466</v>
       </c>
       <c r="C96">
-        <v>60.15808988404617</v>
+        <v>60.245611331764806</v>
       </c>
       <c r="D96">
-        <v>1.9118952552866653</v>
+        <v>0.29773021801726601</v>
       </c>
       <c r="F96" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G96">
-        <v>60.15808988404617</v>
+        <v>60.245611331764806</v>
       </c>
       <c r="H96">
-        <v>1.9118952552866653</v>
+        <v>0.29773021801726601</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -27069,19 +27060,19 @@
         <v>467</v>
       </c>
       <c r="C97">
-        <v>60.245611331764806</v>
+        <v>54.648501411548963</v>
       </c>
       <c r="D97">
-        <v>0.29773021801726601</v>
+        <v>0.66091145601300771</v>
       </c>
       <c r="F97" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G97">
-        <v>60.245611331764806</v>
+        <v>54.648501411548963</v>
       </c>
       <c r="H97">
-        <v>0.29773021801726601</v>
+        <v>0.66091145601300771</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -27089,19 +27080,19 @@
         <v>468</v>
       </c>
       <c r="C98">
-        <v>54.648501411548963</v>
+        <v>55.343778686593453</v>
       </c>
       <c r="D98">
-        <v>0.66091145601300771</v>
+        <v>-0.97158481285588583</v>
       </c>
       <c r="F98" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G98">
-        <v>54.648501411548963</v>
+        <v>55.343778686593453</v>
       </c>
       <c r="H98">
-        <v>0.66091145601300771</v>
+        <v>-0.97158481285588583</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -27109,19 +27100,19 @@
         <v>469</v>
       </c>
       <c r="C99">
-        <v>55.343778686593453</v>
+        <v>56.068708171275809</v>
       </c>
       <c r="D99">
-        <v>-0.97158481285588583</v>
+        <v>0.35064041968340171</v>
       </c>
       <c r="F99" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G99">
-        <v>55.343778686593453</v>
+        <v>56.068708171275809</v>
       </c>
       <c r="H99">
-        <v>-0.97158481285588583</v>
+        <v>0.35064041968340171</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -27129,19 +27120,19 @@
         <v>470</v>
       </c>
       <c r="C100">
-        <v>56.068708171275809</v>
+        <v>58.82570158307206</v>
       </c>
       <c r="D100">
-        <v>0.35064041968340171</v>
+        <v>-2.2384830300988661</v>
       </c>
       <c r="F100" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G100">
-        <v>56.068708171275809</v>
+        <v>58.82570158307206</v>
       </c>
       <c r="H100">
-        <v>0.35064041968340171</v>
+        <v>-2.2384830300988661</v>
       </c>
     </row>
     <row r="101" spans="2:8">
@@ -27149,19 +27140,19 @@
         <v>471</v>
       </c>
       <c r="C101">
-        <v>58.82570158307206</v>
+        <v>57.195094426222468</v>
       </c>
       <c r="D101">
-        <v>-2.2384830300988661</v>
+        <v>-0.85050624950541776</v>
       </c>
       <c r="F101" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G101">
-        <v>58.82570158307206</v>
+        <v>57.195094426222468</v>
       </c>
       <c r="H101">
-        <v>-2.2384830300988661</v>
+        <v>-0.85050624950541776</v>
       </c>
     </row>
     <row r="102" spans="2:8">
@@ -27169,19 +27160,19 @@
         <v>472</v>
       </c>
       <c r="C102">
-        <v>57.195094426222468</v>
+        <v>57.580272910695001</v>
       </c>
       <c r="D102">
-        <v>-0.85050624950541776</v>
+        <v>1.2612731746968058</v>
       </c>
       <c r="F102" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G102">
-        <v>57.195094426222468</v>
+        <v>57.580272910695001</v>
       </c>
       <c r="H102">
-        <v>-0.85050624950541776</v>
+        <v>1.2612731746968058</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -27189,38 +27180,18 @@
         <v>473</v>
       </c>
       <c r="C103">
-        <v>57.580272910695001</v>
+        <v>58.618082550581519</v>
       </c>
       <c r="D103">
-        <v>1.2612731746968058</v>
+        <v>9.2134350197968007E-2</v>
       </c>
       <c r="F103" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G103">
-        <v>57.580272910695001</v>
+        <v>58.618082550581519</v>
       </c>
       <c r="H103">
-        <v>1.2612731746968058</v>
-      </c>
-    </row>
-    <row r="104" spans="2:8">
-      <c r="B104" t="s">
-        <v>474</v>
-      </c>
-      <c r="C104">
-        <v>58.618082550581519</v>
-      </c>
-      <c r="D104">
-        <v>9.2134350197968007E-2</v>
-      </c>
-      <c r="F104" t="s">
-        <v>678</v>
-      </c>
-      <c r="G104">
-        <v>58.618082550581519</v>
-      </c>
-      <c r="H104">
         <v>9.2134350197968007E-2</v>
       </c>
     </row>
@@ -27230,8 +27201,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95D8DA57-7767-4E95-ABD8-938913354E8E}">
-  <dimension ref="B9:L104"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4D0AA7-6197-4E5F-85E2-4FD8E7873D96}">
+  <dimension ref="B9:L103"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:12">
@@ -27288,19 +27259,19 @@
         <v>381</v>
       </c>
       <c r="G11" t="s">
+        <v>474</v>
+      </c>
+      <c r="H11" t="s">
         <v>475</v>
       </c>
-      <c r="H11" t="s">
-        <v>476</v>
-      </c>
       <c r="J11" t="s">
+        <v>486</v>
+      </c>
+      <c r="K11" t="s">
         <v>487</v>
       </c>
-      <c r="K11" t="s">
-        <v>488</v>
-      </c>
       <c r="L11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -27317,19 +27288,19 @@
         <v>382</v>
       </c>
       <c r="G12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -27346,19 +27317,19 @@
         <v>383</v>
       </c>
       <c r="G13" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -27375,19 +27346,19 @@
         <v>384</v>
       </c>
       <c r="G14" t="s">
+        <v>474</v>
+      </c>
+      <c r="H14" t="s">
         <v>475</v>
       </c>
-      <c r="H14" t="s">
-        <v>476</v>
-      </c>
       <c r="J14" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -27404,19 +27375,19 @@
         <v>385</v>
       </c>
       <c r="G15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J15" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -27433,19 +27404,19 @@
         <v>386</v>
       </c>
       <c r="G16" t="s">
+        <v>474</v>
+      </c>
+      <c r="H16" t="s">
         <v>475</v>
       </c>
-      <c r="H16" t="s">
-        <v>478</v>
-      </c>
       <c r="J16" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K16" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L16" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -27462,19 +27433,19 @@
         <v>387</v>
       </c>
       <c r="G17" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H17" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="J17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -27491,19 +27462,19 @@
         <v>388</v>
       </c>
       <c r="G18" t="s">
+        <v>474</v>
+      </c>
+      <c r="H18" t="s">
         <v>475</v>
       </c>
-      <c r="H18" t="s">
-        <v>480</v>
-      </c>
       <c r="J18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -27520,19 +27491,19 @@
         <v>389</v>
       </c>
       <c r="G19" t="s">
+        <v>474</v>
+      </c>
+      <c r="H19" t="s">
         <v>475</v>
       </c>
-      <c r="H19" t="s">
-        <v>478</v>
-      </c>
       <c r="J19" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K19" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L19" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -27549,19 +27520,19 @@
         <v>390</v>
       </c>
       <c r="G20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H20" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -27578,19 +27549,19 @@
         <v>391</v>
       </c>
       <c r="G21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H21" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J21" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K21" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L21" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -27607,19 +27578,19 @@
         <v>392</v>
       </c>
       <c r="G22" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H22" t="s">
         <v>479</v>
       </c>
       <c r="J22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K22" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L22" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -27636,19 +27607,19 @@
         <v>393</v>
       </c>
       <c r="G23" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J23" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -27665,19 +27636,19 @@
         <v>394</v>
       </c>
       <c r="G24" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H24" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J24" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K24" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L24" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -27694,19 +27665,19 @@
         <v>395</v>
       </c>
       <c r="G25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H25" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J25" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -27723,19 +27694,19 @@
         <v>396</v>
       </c>
       <c r="G26" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H26" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J26" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K26" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L26" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -27752,19 +27723,19 @@
         <v>397</v>
       </c>
       <c r="G27" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H27" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J27" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K27" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L27" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -27781,19 +27752,19 @@
         <v>398</v>
       </c>
       <c r="G28" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H28" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J28" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K28" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L28" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -27810,19 +27781,19 @@
         <v>399</v>
       </c>
       <c r="G29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H29" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J29" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K29" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L29" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -27839,19 +27810,19 @@
         <v>400</v>
       </c>
       <c r="G30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H30" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="J30" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K30" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L30" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -27868,19 +27839,19 @@
         <v>401</v>
       </c>
       <c r="G31" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H31" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="J31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -27897,19 +27868,19 @@
         <v>402</v>
       </c>
       <c r="G32" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H32" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J32" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -27926,19 +27897,19 @@
         <v>403</v>
       </c>
       <c r="G33" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H33" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="J33" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K33" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L33" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -27955,19 +27926,19 @@
         <v>404</v>
       </c>
       <c r="G34" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H34" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J34" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K34" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L34" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -27984,19 +27955,19 @@
         <v>405</v>
       </c>
       <c r="G35" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H35" t="s">
         <v>484</v>
       </c>
       <c r="J35" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K35" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L35" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -28013,19 +27984,19 @@
         <v>406</v>
       </c>
       <c r="G36" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H36" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="J36" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L36" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -28042,19 +28013,19 @@
         <v>407</v>
       </c>
       <c r="G37" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H37" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="J37" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K37" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L37" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -28071,19 +28042,19 @@
         <v>408</v>
       </c>
       <c r="G38" t="s">
+        <v>474</v>
+      </c>
+      <c r="H38" t="s">
         <v>475</v>
       </c>
-      <c r="H38" t="s">
-        <v>485</v>
-      </c>
       <c r="J38" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K38" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L38" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -28100,19 +28071,19 @@
         <v>409</v>
       </c>
       <c r="G39" t="s">
+        <v>474</v>
+      </c>
+      <c r="H39" t="s">
         <v>475</v>
       </c>
-      <c r="H39" t="s">
-        <v>478</v>
-      </c>
       <c r="J39" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K39" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L39" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -28129,19 +28100,19 @@
         <v>410</v>
       </c>
       <c r="G40" t="s">
+        <v>474</v>
+      </c>
+      <c r="H40" t="s">
         <v>475</v>
       </c>
-      <c r="H40" t="s">
-        <v>478</v>
-      </c>
       <c r="J40" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K40" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L40" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -28158,19 +28129,19 @@
         <v>411</v>
       </c>
       <c r="G41" t="s">
+        <v>474</v>
+      </c>
+      <c r="H41" t="s">
         <v>475</v>
       </c>
-      <c r="H41" t="s">
-        <v>478</v>
-      </c>
       <c r="J41" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K41" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L41" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -28187,19 +28158,19 @@
         <v>412</v>
       </c>
       <c r="G42" t="s">
+        <v>474</v>
+      </c>
+      <c r="H42" t="s">
         <v>475</v>
       </c>
-      <c r="H42" t="s">
-        <v>478</v>
-      </c>
       <c r="J42" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -28216,19 +28187,19 @@
         <v>413</v>
       </c>
       <c r="G43" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H43" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="J43" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K43" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L43" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -28245,19 +28216,19 @@
         <v>414</v>
       </c>
       <c r="G44" t="s">
+        <v>474</v>
+      </c>
+      <c r="H44" t="s">
         <v>475</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>486</v>
       </c>
-      <c r="J44" t="s">
-        <v>487</v>
-      </c>
       <c r="K44" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L44" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -28274,19 +28245,19 @@
         <v>415</v>
       </c>
       <c r="G45" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H45" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J45" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -28303,19 +28274,19 @@
         <v>416</v>
       </c>
       <c r="G46" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H46" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J46" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K46" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L46" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -28332,19 +28303,19 @@
         <v>417</v>
       </c>
       <c r="G47" t="s">
+        <v>474</v>
+      </c>
+      <c r="H47" t="s">
         <v>475</v>
       </c>
-      <c r="H47" t="s">
-        <v>480</v>
-      </c>
       <c r="J47" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K47" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L47" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -28361,19 +28332,19 @@
         <v>418</v>
       </c>
       <c r="G48" t="s">
+        <v>474</v>
+      </c>
+      <c r="H48" t="s">
         <v>475</v>
       </c>
-      <c r="H48" t="s">
-        <v>478</v>
-      </c>
       <c r="J48" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K48" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L48" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -28390,19 +28361,19 @@
         <v>419</v>
       </c>
       <c r="G49" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H49" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="J49" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K49" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L49" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -28419,19 +28390,19 @@
         <v>420</v>
       </c>
       <c r="G50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L50" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -28448,19 +28419,19 @@
         <v>421</v>
       </c>
       <c r="G51" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H51" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="J51" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K51" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L51" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -28477,19 +28448,19 @@
         <v>422</v>
       </c>
       <c r="G52" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H52" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J52" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K52" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L52" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -28506,19 +28477,19 @@
         <v>423</v>
       </c>
       <c r="G53" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H53" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="J53" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K53" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L53" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -28535,19 +28506,19 @@
         <v>424</v>
       </c>
       <c r="G54" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H54" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J54" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K54" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L54" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -28564,19 +28535,19 @@
         <v>425</v>
       </c>
       <c r="G55" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H55" t="s">
         <v>476</v>
       </c>
       <c r="J55" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K55" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L55" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -28593,19 +28564,19 @@
         <v>426</v>
       </c>
       <c r="G56" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H56" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="J56" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K56" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L56" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -28622,19 +28593,19 @@
         <v>427</v>
       </c>
       <c r="G57" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H57" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J57" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K57" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L57" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -28651,19 +28622,19 @@
         <v>428</v>
       </c>
       <c r="G58" t="s">
+        <v>474</v>
+      </c>
+      <c r="H58" t="s">
         <v>475</v>
       </c>
-      <c r="H58" t="s">
-        <v>484</v>
-      </c>
       <c r="J58" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K58" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L58" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -28680,19 +28651,19 @@
         <v>429</v>
       </c>
       <c r="G59" t="s">
+        <v>474</v>
+      </c>
+      <c r="H59" t="s">
         <v>475</v>
       </c>
-      <c r="H59" t="s">
-        <v>478</v>
-      </c>
       <c r="J59" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K59" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L59" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -28709,19 +28680,19 @@
         <v>430</v>
       </c>
       <c r="G60" t="s">
+        <v>474</v>
+      </c>
+      <c r="H60" t="s">
         <v>475</v>
       </c>
-      <c r="H60" t="s">
-        <v>478</v>
-      </c>
       <c r="J60" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K60" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L60" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -28738,19 +28709,19 @@
         <v>431</v>
       </c>
       <c r="G61" t="s">
+        <v>474</v>
+      </c>
+      <c r="H61" t="s">
         <v>475</v>
       </c>
-      <c r="H61" t="s">
-        <v>478</v>
-      </c>
       <c r="J61" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K61" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L61" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -28767,19 +28738,19 @@
         <v>432</v>
       </c>
       <c r="G62" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H62" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J62" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K62" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="L62" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -28796,19 +28767,19 @@
         <v>433</v>
       </c>
       <c r="G63" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H63" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J63" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K63" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="L63" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -28825,19 +28796,19 @@
         <v>434</v>
       </c>
       <c r="G64" t="s">
+        <v>474</v>
+      </c>
+      <c r="H64" t="s">
         <v>475</v>
       </c>
-      <c r="H64" t="s">
-        <v>480</v>
-      </c>
       <c r="J64" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K64" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L64" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -28854,19 +28825,19 @@
         <v>435</v>
       </c>
       <c r="G65" t="s">
+        <v>474</v>
+      </c>
+      <c r="H65" t="s">
         <v>475</v>
       </c>
-      <c r="H65" t="s">
-        <v>478</v>
-      </c>
       <c r="J65" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K65" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L65" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -28883,19 +28854,19 @@
         <v>436</v>
       </c>
       <c r="G66" t="s">
+        <v>474</v>
+      </c>
+      <c r="H66" t="s">
         <v>475</v>
       </c>
-      <c r="H66" t="s">
-        <v>478</v>
-      </c>
       <c r="J66" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K66" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L66" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -28912,19 +28883,19 @@
         <v>437</v>
       </c>
       <c r="G67" t="s">
+        <v>474</v>
+      </c>
+      <c r="H67" t="s">
         <v>475</v>
       </c>
-      <c r="H67" t="s">
-        <v>478</v>
-      </c>
       <c r="J67" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K67" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L67" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -28941,19 +28912,19 @@
         <v>438</v>
       </c>
       <c r="G68" t="s">
+        <v>474</v>
+      </c>
+      <c r="H68" t="s">
         <v>475</v>
       </c>
-      <c r="H68" t="s">
-        <v>478</v>
-      </c>
       <c r="J68" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K68" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L68" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -28970,19 +28941,19 @@
         <v>439</v>
       </c>
       <c r="G69" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H69" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="J69" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K69" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L69" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -28999,19 +28970,19 @@
         <v>440</v>
       </c>
       <c r="G70" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H70" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="J70" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K70" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L70" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -29028,19 +28999,19 @@
         <v>441</v>
       </c>
       <c r="G71" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H71" t="s">
+        <v>485</v>
+      </c>
+      <c r="J71" t="s">
         <v>486</v>
       </c>
-      <c r="J71" t="s">
-        <v>487</v>
-      </c>
       <c r="K71" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L71" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -29057,19 +29028,19 @@
         <v>442</v>
       </c>
       <c r="G72" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H72" t="s">
+        <v>485</v>
+      </c>
+      <c r="J72" t="s">
         <v>486</v>
       </c>
-      <c r="J72" t="s">
-        <v>487</v>
-      </c>
       <c r="K72" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -29086,19 +29057,19 @@
         <v>443</v>
       </c>
       <c r="G73" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H73" t="s">
+        <v>485</v>
+      </c>
+      <c r="J73" t="s">
         <v>486</v>
       </c>
-      <c r="J73" t="s">
-        <v>487</v>
-      </c>
       <c r="K73" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L73" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -29115,19 +29086,19 @@
         <v>444</v>
       </c>
       <c r="G74" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H74" t="s">
+        <v>485</v>
+      </c>
+      <c r="J74" t="s">
         <v>486</v>
       </c>
-      <c r="J74" t="s">
-        <v>487</v>
-      </c>
       <c r="K74" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -29144,19 +29115,19 @@
         <v>445</v>
       </c>
       <c r="G75" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H75" t="s">
+        <v>485</v>
+      </c>
+      <c r="J75" t="s">
         <v>486</v>
       </c>
-      <c r="J75" t="s">
-        <v>487</v>
-      </c>
       <c r="K75" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L75" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -29173,19 +29144,19 @@
         <v>446</v>
       </c>
       <c r="G76" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H76" t="s">
+        <v>485</v>
+      </c>
+      <c r="J76" t="s">
         <v>486</v>
       </c>
-      <c r="J76" t="s">
-        <v>487</v>
-      </c>
       <c r="K76" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L76" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -29202,19 +29173,19 @@
         <v>447</v>
       </c>
       <c r="G77" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H77" t="s">
+        <v>485</v>
+      </c>
+      <c r="J77" t="s">
         <v>486</v>
       </c>
-      <c r="J77" t="s">
-        <v>487</v>
-      </c>
       <c r="K77" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="L77" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -29231,19 +29202,19 @@
         <v>448</v>
       </c>
       <c r="G78" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H78" t="s">
+        <v>485</v>
+      </c>
+      <c r="J78" t="s">
         <v>486</v>
       </c>
-      <c r="J78" t="s">
-        <v>487</v>
-      </c>
       <c r="K78" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L78" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -29260,19 +29231,19 @@
         <v>449</v>
       </c>
       <c r="G79" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H79" t="s">
+        <v>485</v>
+      </c>
+      <c r="J79" t="s">
         <v>486</v>
       </c>
-      <c r="J79" t="s">
-        <v>487</v>
-      </c>
       <c r="K79" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L79" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -29289,19 +29260,19 @@
         <v>450</v>
       </c>
       <c r="G80" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H80" t="s">
+        <v>485</v>
+      </c>
+      <c r="J80" t="s">
         <v>486</v>
       </c>
-      <c r="J80" t="s">
-        <v>487</v>
-      </c>
       <c r="K80" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L80" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -29318,19 +29289,19 @@
         <v>451</v>
       </c>
       <c r="G81" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H81" t="s">
+        <v>485</v>
+      </c>
+      <c r="J81" t="s">
         <v>486</v>
       </c>
-      <c r="J81" t="s">
-        <v>487</v>
-      </c>
       <c r="K81" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L81" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -29347,19 +29318,19 @@
         <v>452</v>
       </c>
       <c r="G82" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H82" t="s">
+        <v>485</v>
+      </c>
+      <c r="J82" t="s">
         <v>486</v>
       </c>
-      <c r="J82" t="s">
-        <v>487</v>
-      </c>
       <c r="K82" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="L82" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -29376,19 +29347,19 @@
         <v>453</v>
       </c>
       <c r="G83" t="s">
+        <v>474</v>
+      </c>
+      <c r="H83" t="s">
         <v>475</v>
       </c>
-      <c r="H83" t="s">
+      <c r="J83" t="s">
         <v>486</v>
       </c>
-      <c r="J83" t="s">
-        <v>487</v>
-      </c>
       <c r="K83" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="L83" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -29405,19 +29376,19 @@
         <v>454</v>
       </c>
       <c r="G84" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H84" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="J84" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K84" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="L84" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -29434,19 +29405,19 @@
         <v>455</v>
       </c>
       <c r="G85" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H85" t="s">
+        <v>485</v>
+      </c>
+      <c r="J85" t="s">
         <v>486</v>
       </c>
-      <c r="J85" t="s">
-        <v>487</v>
-      </c>
       <c r="K85" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L85" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -29463,19 +29434,19 @@
         <v>456</v>
       </c>
       <c r="G86" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H86" t="s">
+        <v>485</v>
+      </c>
+      <c r="J86" t="s">
         <v>486</v>
       </c>
-      <c r="J86" t="s">
-        <v>487</v>
-      </c>
       <c r="K86" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="L86" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -29492,19 +29463,19 @@
         <v>457</v>
       </c>
       <c r="G87" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H87" t="s">
+        <v>485</v>
+      </c>
+      <c r="J87" t="s">
         <v>486</v>
       </c>
-      <c r="J87" t="s">
-        <v>487</v>
-      </c>
       <c r="K87" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="L87" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -29521,19 +29492,19 @@
         <v>458</v>
       </c>
       <c r="G88" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H88" t="s">
+        <v>485</v>
+      </c>
+      <c r="J88" t="s">
         <v>486</v>
       </c>
-      <c r="J88" t="s">
-        <v>487</v>
-      </c>
       <c r="K88" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L88" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -29550,19 +29521,19 @@
         <v>459</v>
       </c>
       <c r="G89" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H89" t="s">
+        <v>485</v>
+      </c>
+      <c r="J89" t="s">
         <v>486</v>
       </c>
-      <c r="J89" t="s">
-        <v>487</v>
-      </c>
       <c r="K89" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L89" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -29579,19 +29550,19 @@
         <v>460</v>
       </c>
       <c r="G90" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H90" t="s">
+        <v>485</v>
+      </c>
+      <c r="J90" t="s">
         <v>486</v>
       </c>
-      <c r="J90" t="s">
-        <v>487</v>
-      </c>
       <c r="K90" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L90" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -29608,19 +29579,19 @@
         <v>461</v>
       </c>
       <c r="G91" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H91" t="s">
+        <v>485</v>
+      </c>
+      <c r="J91" t="s">
         <v>486</v>
       </c>
-      <c r="J91" t="s">
-        <v>487</v>
-      </c>
       <c r="K91" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L91" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -29637,19 +29608,19 @@
         <v>462</v>
       </c>
       <c r="G92" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H92" t="s">
+        <v>485</v>
+      </c>
+      <c r="J92" t="s">
         <v>486</v>
       </c>
-      <c r="J92" t="s">
-        <v>487</v>
-      </c>
       <c r="K92" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L92" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -29666,19 +29637,19 @@
         <v>463</v>
       </c>
       <c r="G93" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H93" t="s">
+        <v>485</v>
+      </c>
+      <c r="J93" t="s">
         <v>486</v>
       </c>
-      <c r="J93" t="s">
-        <v>487</v>
-      </c>
       <c r="K93" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L93" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -29695,19 +29666,19 @@
         <v>464</v>
       </c>
       <c r="G94" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H94" t="s">
+        <v>485</v>
+      </c>
+      <c r="J94" t="s">
         <v>486</v>
       </c>
-      <c r="J94" t="s">
-        <v>487</v>
-      </c>
       <c r="K94" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="L94" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -29724,19 +29695,19 @@
         <v>465</v>
       </c>
       <c r="G95" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H95" t="s">
+        <v>485</v>
+      </c>
+      <c r="J95" t="s">
         <v>486</v>
       </c>
-      <c r="J95" t="s">
-        <v>487</v>
-      </c>
       <c r="K95" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L95" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -29753,19 +29724,19 @@
         <v>466</v>
       </c>
       <c r="G96" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H96" t="s">
+        <v>485</v>
+      </c>
+      <c r="J96" t="s">
         <v>486</v>
       </c>
-      <c r="J96" t="s">
-        <v>487</v>
-      </c>
       <c r="K96" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L96" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -29782,19 +29753,19 @@
         <v>467</v>
       </c>
       <c r="G97" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H97" t="s">
+        <v>485</v>
+      </c>
+      <c r="J97" t="s">
         <v>486</v>
       </c>
-      <c r="J97" t="s">
-        <v>487</v>
-      </c>
       <c r="K97" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L97" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -29811,19 +29782,19 @@
         <v>468</v>
       </c>
       <c r="G98" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H98" t="s">
+        <v>485</v>
+      </c>
+      <c r="J98" t="s">
         <v>486</v>
       </c>
-      <c r="J98" t="s">
-        <v>487</v>
-      </c>
       <c r="K98" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L98" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -29840,19 +29811,19 @@
         <v>469</v>
       </c>
       <c r="G99" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H99" t="s">
+        <v>485</v>
+      </c>
+      <c r="J99" t="s">
         <v>486</v>
       </c>
-      <c r="J99" t="s">
-        <v>487</v>
-      </c>
       <c r="K99" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L99" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -29869,19 +29840,19 @@
         <v>470</v>
       </c>
       <c r="G100" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H100" t="s">
+        <v>485</v>
+      </c>
+      <c r="J100" t="s">
         <v>486</v>
       </c>
-      <c r="J100" t="s">
-        <v>487</v>
-      </c>
       <c r="K100" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="L100" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -29898,19 +29869,19 @@
         <v>471</v>
       </c>
       <c r="G101" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H101" t="s">
+        <v>485</v>
+      </c>
+      <c r="J101" t="s">
         <v>486</v>
       </c>
-      <c r="J101" t="s">
-        <v>487</v>
-      </c>
       <c r="K101" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L101" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -29927,19 +29898,19 @@
         <v>472</v>
       </c>
       <c r="G102" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H102" t="s">
+        <v>485</v>
+      </c>
+      <c r="J102" t="s">
         <v>486</v>
       </c>
-      <c r="J102" t="s">
-        <v>487</v>
-      </c>
       <c r="K102" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="L102" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -29956,48 +29927,19 @@
         <v>473</v>
       </c>
       <c r="G103" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H103" t="s">
+        <v>485</v>
+      </c>
+      <c r="J103" t="s">
         <v>486</v>
       </c>
-      <c r="J103" t="s">
-        <v>487</v>
-      </c>
       <c r="K103" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L103" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="104" spans="2:12">
-      <c r="B104" t="s">
-        <v>380</v>
-      </c>
-      <c r="C104" t="s">
-        <v>474</v>
-      </c>
-      <c r="D104" t="s">
-        <v>474</v>
-      </c>
-      <c r="F104" t="s">
-        <v>474</v>
-      </c>
-      <c r="G104" t="s">
-        <v>475</v>
-      </c>
-      <c r="H104" t="s">
-        <v>486</v>
-      </c>
-      <c r="J104" t="s">
-        <v>487</v>
-      </c>
-      <c r="K104" t="s">
-        <v>581</v>
-      </c>
-      <c r="L104" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
